--- a/templates/productie/productie_bodem_template.xlsx
+++ b/templates/productie/productie_bodem_template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12918" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12915" uniqueCount="2045">
   <si>
     <t>naam</t>
   </si>
@@ -6127,25 +6127,25 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-02-10 16:31:00.737604</t>
+    <t>2026-03-31 16:50:38.890677</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.2.3</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>9.4.3</t>
+    <t>10.1.0</t>
   </si>
   <si>
     <t>schema-version</t>
   </si>
   <si>
-    <t>5.9.0</t>
+    <t>5.10.0</t>
   </si>
   <si>
     <t>mode</t>
@@ -47811,7 +47811,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="3" customWidth="1"/>
@@ -47871,10 +47871,9 @@
     <col min="57" max="57" width="34.7109375" style="3" customWidth="1"/>
     <col min="58" max="58" width="48.7109375" style="3" customWidth="1"/>
     <col min="59" max="59" width="40.7109375" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" hidden="1">
+    <row r="1" spans="1:59" hidden="1">
       <c r="A1" s="7" t="s">
         <v>1756</v>
       </c>
@@ -48052,11 +48051,8 @@
       <c r="BG1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" hidden="1">
+    </row>
+    <row r="2" spans="1:59" hidden="1">
       <c r="A2" s="8" t="s">
         <v>1757</v>
       </c>
@@ -48144,11 +48140,8 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="1" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" hidden="1">
+    </row>
+    <row r="3" spans="1:59" hidden="1">
       <c r="A3" s="8" t="s">
         <v>1757</v>
       </c>
@@ -48263,7 +48256,7 @@
       </c>
       <c r="BG3" s="1"/>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:59" hidden="1">
       <c r="E4" s="8" t="s">
         <v>78</v>
       </c>
@@ -48346,7 +48339,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:60" hidden="1">
+    <row r="5" spans="1:59" hidden="1">
       <c r="K5" s="8" t="s">
         <v>1773</v>
       </c>
@@ -48399,7 +48392,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:59">
       <c r="A6" s="7" t="s">
         <v>1756</v>
       </c>
@@ -48576,9 +48569,6 @@
       </c>
       <c r="BG6" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>1764</v>
       </c>
     </row>
   </sheetData>

--- a/templates/productie/productie_bodem_template.xlsx
+++ b/templates/productie/productie_bodem_template.xlsx
@@ -6127,13 +6127,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:50:38.890677</t>
+    <t>2026-05-06 16:21:12.168290</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>

--- a/templates/productie/productie_bodem_template.xlsx
+++ b/templates/productie/productie_bodem_template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12915" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12919" uniqueCount="2047">
   <si>
     <t>naam</t>
   </si>
@@ -5833,6 +5833,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -6127,19 +6133,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:12.168290</t>
+    <t>2026-05-19 11:28:43.640697</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>
@@ -6662,7 +6668,7 @@
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="Table45" displayName="Table45" ref="CK3:CL12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="Table45" displayName="Table45" ref="CK3:CL14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -7238,7 +7244,7 @@
       <c r="CC1" s="1"/>
       <c r="CD1" s="1"/>
       <c r="CE1" s="1" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="CF1" s="1"/>
       <c r="CG1" s="1"/>
@@ -7254,7 +7260,7 @@
       <c r="CQ1" s="1"/>
       <c r="CR1" s="1"/>
       <c r="CS1" s="1" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="CT1" s="1"/>
       <c r="CU1" s="1"/>
@@ -7470,15 +7476,15 @@
       </c>
       <c r="CR2" s="1"/>
       <c r="CS2" s="1" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="CT2" s="1"/>
       <c r="CU2" s="1" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="CV2" s="1"/>
       <c r="CW2" s="1" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="CX2" s="1"/>
       <c r="CY2" s="1" t="s">
@@ -8132,13 +8138,13 @@
         <v>83</v>
       </c>
       <c r="CM4" s="2" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="CN4" t="s">
         <v>83</v>
       </c>
       <c r="CO4" s="2" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="CP4" t="s">
         <v>83</v>
@@ -8186,7 +8192,7 @@
         <v>83</v>
       </c>
       <c r="DE4" s="2" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="DF4" t="s">
         <v>83</v>
@@ -8482,13 +8488,13 @@
         <v>83</v>
       </c>
       <c r="CM5" s="2" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="CN5" t="s">
         <v>83</v>
       </c>
       <c r="CO5" s="2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="CP5" t="s">
         <v>83</v>
@@ -8536,7 +8542,7 @@
         <v>83</v>
       </c>
       <c r="DE5" s="2" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="DF5" t="s">
         <v>83</v>
@@ -8802,13 +8808,13 @@
         <v>83</v>
       </c>
       <c r="CM6" s="2" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="CN6" t="s">
         <v>83</v>
       </c>
       <c r="CO6" s="2" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="CP6" t="s">
         <v>83</v>
@@ -8856,7 +8862,7 @@
         <v>83</v>
       </c>
       <c r="DE6" s="2" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="DF6" t="s">
         <v>83</v>
@@ -9050,7 +9056,7 @@
         <v>83</v>
       </c>
       <c r="CM7" s="2" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="CN7" t="s">
         <v>83</v>
@@ -9274,7 +9280,7 @@
         <v>83</v>
       </c>
       <c r="CM8" s="2" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="CN8" t="s">
         <v>83</v>
@@ -9468,7 +9474,7 @@
         <v>83</v>
       </c>
       <c r="CM9" s="2" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="CN9" t="s">
         <v>83</v>
@@ -9656,7 +9662,7 @@
         <v>83</v>
       </c>
       <c r="CM10" s="2" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="CN10" t="s">
         <v>83</v>
@@ -9844,7 +9850,7 @@
         <v>83</v>
       </c>
       <c r="CM11" s="2" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="CN11" t="s">
         <v>83</v>
@@ -10032,7 +10038,7 @@
         <v>83</v>
       </c>
       <c r="CM12" s="2" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="CN12" t="s">
         <v>83</v>
@@ -10213,8 +10219,14 @@
       <c r="CJ13" t="s">
         <v>83</v>
       </c>
+      <c r="CK13" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>83</v>
+      </c>
       <c r="CM13" s="2" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="CN13" t="s">
         <v>83</v>
@@ -10395,8 +10407,14 @@
       <c r="CJ14" t="s">
         <v>83</v>
       </c>
+      <c r="CK14" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="CL14" t="s">
+        <v>83</v>
+      </c>
       <c r="CM14" s="2" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="CN14" t="s">
         <v>83</v>
@@ -10578,7 +10596,7 @@
         <v>83</v>
       </c>
       <c r="CM15" s="2" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="CN15" t="s">
         <v>83</v>
@@ -10760,7 +10778,7 @@
         <v>83</v>
       </c>
       <c r="CM16" s="2" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="CN16" t="s">
         <v>83</v>
@@ -10942,7 +10960,7 @@
         <v>83</v>
       </c>
       <c r="CM17" s="2" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="CN17" t="s">
         <v>83</v>
@@ -11112,7 +11130,7 @@
         <v>83</v>
       </c>
       <c r="CM18" s="2" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="CN18" t="s">
         <v>83</v>
@@ -11276,7 +11294,7 @@
         <v>83</v>
       </c>
       <c r="CM19" s="2" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="CN19" t="s">
         <v>83</v>
@@ -11440,7 +11458,7 @@
         <v>83</v>
       </c>
       <c r="CM20" s="2" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="CN20" t="s">
         <v>83</v>
@@ -11592,7 +11610,7 @@
         <v>83</v>
       </c>
       <c r="CM21" s="2" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="CN21" t="s">
         <v>83</v>
@@ -11738,7 +11756,7 @@
         <v>83</v>
       </c>
       <c r="CM22" s="2" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="CN22" t="s">
         <v>83</v>
@@ -11884,7 +11902,7 @@
         <v>83</v>
       </c>
       <c r="CM23" s="2" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="CN23" t="s">
         <v>83</v>
@@ -12024,7 +12042,7 @@
         <v>83</v>
       </c>
       <c r="CM24" s="2" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="CN24" t="s">
         <v>83</v>
@@ -12164,7 +12182,7 @@
         <v>83</v>
       </c>
       <c r="CM25" s="2" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="CN25" t="s">
         <v>83</v>
@@ -12304,7 +12322,7 @@
         <v>83</v>
       </c>
       <c r="CM26" s="2" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="CN26" t="s">
         <v>83</v>
@@ -12444,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="CM27" s="2" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="CN27" t="s">
         <v>83</v>
@@ -12584,7 +12602,7 @@
         <v>83</v>
       </c>
       <c r="CM28" s="2" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="CN28" t="s">
         <v>83</v>
@@ -12724,7 +12742,7 @@
         <v>83</v>
       </c>
       <c r="CM29" s="2" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="CN29" t="s">
         <v>83</v>
@@ -12858,7 +12876,7 @@
         <v>83</v>
       </c>
       <c r="CM30" s="2" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="CN30" t="s">
         <v>83</v>
@@ -12992,7 +13010,7 @@
         <v>83</v>
       </c>
       <c r="CM31" s="2" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="CN31" t="s">
         <v>83</v>
@@ -13126,7 +13144,7 @@
         <v>83</v>
       </c>
       <c r="CM32" s="2" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="CN32" t="s">
         <v>83</v>
@@ -13260,7 +13278,7 @@
         <v>83</v>
       </c>
       <c r="CM33" s="2" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="CN33" t="s">
         <v>83</v>
@@ -13394,7 +13412,7 @@
         <v>83</v>
       </c>
       <c r="CM34" s="2" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="CN34" t="s">
         <v>83</v>
@@ -13528,7 +13546,7 @@
         <v>83</v>
       </c>
       <c r="CM35" s="2" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="CN35" t="s">
         <v>83</v>
@@ -13662,7 +13680,7 @@
         <v>83</v>
       </c>
       <c r="CM36" s="2" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="CN36" t="s">
         <v>83</v>
@@ -13796,7 +13814,7 @@
         <v>83</v>
       </c>
       <c r="CM37" s="2" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="CN37" t="s">
         <v>83</v>
@@ -13930,7 +13948,7 @@
         <v>83</v>
       </c>
       <c r="CM38" s="2" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="CN38" t="s">
         <v>83</v>
@@ -14064,7 +14082,7 @@
         <v>83</v>
       </c>
       <c r="CM39" s="2" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="CN39" t="s">
         <v>83</v>
@@ -14198,7 +14216,7 @@
         <v>83</v>
       </c>
       <c r="CM40" s="2" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="CN40" t="s">
         <v>83</v>
@@ -44394,113 +44412,113 @@
     <hyperlink ref="CK12" r:id="rId32"/>
     <hyperlink ref="CM12" r:id="rId33"/>
     <hyperlink ref="CI13" r:id="rId34"/>
-    <hyperlink ref="CM13" r:id="rId35"/>
-    <hyperlink ref="CI14" r:id="rId36"/>
-    <hyperlink ref="CM14" r:id="rId37"/>
-    <hyperlink ref="CI15" r:id="rId38"/>
-    <hyperlink ref="CM15" r:id="rId39"/>
-    <hyperlink ref="CI16" r:id="rId40"/>
-    <hyperlink ref="CM16" r:id="rId41"/>
-    <hyperlink ref="CI17" r:id="rId42"/>
-    <hyperlink ref="CM17" r:id="rId43"/>
-    <hyperlink ref="CI18" r:id="rId44"/>
-    <hyperlink ref="CM18" r:id="rId45"/>
-    <hyperlink ref="CI19" r:id="rId46"/>
-    <hyperlink ref="CM19" r:id="rId47"/>
-    <hyperlink ref="CI20" r:id="rId48"/>
-    <hyperlink ref="CM20" r:id="rId49"/>
-    <hyperlink ref="CI21" r:id="rId50"/>
-    <hyperlink ref="CM21" r:id="rId51"/>
-    <hyperlink ref="CI22" r:id="rId52"/>
-    <hyperlink ref="CM22" r:id="rId53"/>
-    <hyperlink ref="CI23" r:id="rId54"/>
-    <hyperlink ref="CM23" r:id="rId55"/>
-    <hyperlink ref="CI24" r:id="rId56"/>
-    <hyperlink ref="CM24" r:id="rId57"/>
-    <hyperlink ref="CI25" r:id="rId58"/>
-    <hyperlink ref="CM25" r:id="rId59"/>
-    <hyperlink ref="CI26" r:id="rId60"/>
-    <hyperlink ref="CM26" r:id="rId61"/>
-    <hyperlink ref="CI27" r:id="rId62"/>
-    <hyperlink ref="CM27" r:id="rId63"/>
-    <hyperlink ref="CI28" r:id="rId64"/>
-    <hyperlink ref="CM28" r:id="rId65"/>
-    <hyperlink ref="CI29" r:id="rId66"/>
-    <hyperlink ref="CM29" r:id="rId67"/>
-    <hyperlink ref="CI30" r:id="rId68"/>
-    <hyperlink ref="CM30" r:id="rId69"/>
-    <hyperlink ref="CI31" r:id="rId70"/>
-    <hyperlink ref="CM31" r:id="rId71"/>
-    <hyperlink ref="CI32" r:id="rId72"/>
-    <hyperlink ref="CM32" r:id="rId73"/>
-    <hyperlink ref="CI33" r:id="rId74"/>
-    <hyperlink ref="CM33" r:id="rId75"/>
-    <hyperlink ref="CI34" r:id="rId76"/>
-    <hyperlink ref="CM34" r:id="rId77"/>
-    <hyperlink ref="CI35" r:id="rId78"/>
-    <hyperlink ref="CM35" r:id="rId79"/>
-    <hyperlink ref="CI36" r:id="rId80"/>
-    <hyperlink ref="CM36" r:id="rId81"/>
-    <hyperlink ref="CI37" r:id="rId82"/>
-    <hyperlink ref="CM37" r:id="rId83"/>
-    <hyperlink ref="CI38" r:id="rId84"/>
-    <hyperlink ref="CM38" r:id="rId85"/>
-    <hyperlink ref="CI39" r:id="rId86"/>
-    <hyperlink ref="CM39" r:id="rId87"/>
-    <hyperlink ref="CI40" r:id="rId88"/>
-    <hyperlink ref="CM40" r:id="rId89"/>
-    <hyperlink ref="CI41" r:id="rId90"/>
-    <hyperlink ref="CI42" r:id="rId91"/>
-    <hyperlink ref="CI43" r:id="rId92"/>
-    <hyperlink ref="CI44" r:id="rId93"/>
-    <hyperlink ref="CI45" r:id="rId94"/>
-    <hyperlink ref="CI46" r:id="rId95"/>
-    <hyperlink ref="CI47" r:id="rId96"/>
-    <hyperlink ref="CI48" r:id="rId97"/>
-    <hyperlink ref="CI49" r:id="rId98"/>
-    <hyperlink ref="CI50" r:id="rId99"/>
-    <hyperlink ref="CI51" r:id="rId100"/>
-    <hyperlink ref="CI52" r:id="rId101"/>
-    <hyperlink ref="CI53" r:id="rId102"/>
-    <hyperlink ref="CI54" r:id="rId103"/>
-    <hyperlink ref="CI55" r:id="rId104"/>
-    <hyperlink ref="CI56" r:id="rId105"/>
-    <hyperlink ref="CI57" r:id="rId106"/>
-    <hyperlink ref="CI58" r:id="rId107"/>
-    <hyperlink ref="CI59" r:id="rId108"/>
-    <hyperlink ref="CI60" r:id="rId109"/>
-    <hyperlink ref="CI61" r:id="rId110"/>
-    <hyperlink ref="CI62" r:id="rId111"/>
-    <hyperlink ref="CI63" r:id="rId112"/>
-    <hyperlink ref="CI64" r:id="rId113"/>
-    <hyperlink ref="CI65" r:id="rId114"/>
-    <hyperlink ref="CI66" r:id="rId115"/>
-    <hyperlink ref="CI67" r:id="rId116"/>
-    <hyperlink ref="CI68" r:id="rId117"/>
-    <hyperlink ref="CI69" r:id="rId118"/>
-    <hyperlink ref="CI70" r:id="rId119"/>
-    <hyperlink ref="CI71" r:id="rId120"/>
-    <hyperlink ref="CI72" r:id="rId121"/>
-    <hyperlink ref="CI73" r:id="rId122"/>
-    <hyperlink ref="CI74" r:id="rId123"/>
-    <hyperlink ref="CI75" r:id="rId124"/>
-    <hyperlink ref="CI76" r:id="rId125"/>
-    <hyperlink ref="CI77" r:id="rId126"/>
-    <hyperlink ref="CI78" r:id="rId127"/>
-    <hyperlink ref="CI79" r:id="rId128"/>
-    <hyperlink ref="CI80" r:id="rId129"/>
-    <hyperlink ref="CI81" r:id="rId130"/>
-    <hyperlink ref="CI82" r:id="rId131"/>
-    <hyperlink ref="CI83" r:id="rId132"/>
-    <hyperlink ref="CI84" r:id="rId133"/>
-    <hyperlink ref="CI85" r:id="rId134"/>
-    <hyperlink ref="CI86" r:id="rId135"/>
-    <hyperlink ref="CI87" r:id="rId136"/>
+    <hyperlink ref="CK13" r:id="rId35"/>
+    <hyperlink ref="CM13" r:id="rId36"/>
+    <hyperlink ref="CI14" r:id="rId37"/>
+    <hyperlink ref="CK14" r:id="rId38"/>
+    <hyperlink ref="CM14" r:id="rId39"/>
+    <hyperlink ref="CI15" r:id="rId40"/>
+    <hyperlink ref="CM15" r:id="rId41"/>
+    <hyperlink ref="CI16" r:id="rId42"/>
+    <hyperlink ref="CM16" r:id="rId43"/>
+    <hyperlink ref="CI17" r:id="rId44"/>
+    <hyperlink ref="CM17" r:id="rId45"/>
+    <hyperlink ref="CI18" r:id="rId46"/>
+    <hyperlink ref="CM18" r:id="rId47"/>
+    <hyperlink ref="CI19" r:id="rId48"/>
+    <hyperlink ref="CM19" r:id="rId49"/>
+    <hyperlink ref="CI20" r:id="rId50"/>
+    <hyperlink ref="CM20" r:id="rId51"/>
+    <hyperlink ref="CI21" r:id="rId52"/>
+    <hyperlink ref="CM21" r:id="rId53"/>
+    <hyperlink ref="CI22" r:id="rId54"/>
+    <hyperlink ref="CM22" r:id="rId55"/>
+    <hyperlink ref="CI23" r:id="rId56"/>
+    <hyperlink ref="CM23" r:id="rId57"/>
+    <hyperlink ref="CI24" r:id="rId58"/>
+    <hyperlink ref="CM24" r:id="rId59"/>
+    <hyperlink ref="CI25" r:id="rId60"/>
+    <hyperlink ref="CM25" r:id="rId61"/>
+    <hyperlink ref="CI26" r:id="rId62"/>
+    <hyperlink ref="CM26" r:id="rId63"/>
+    <hyperlink ref="CI27" r:id="rId64"/>
+    <hyperlink ref="CM27" r:id="rId65"/>
+    <hyperlink ref="CI28" r:id="rId66"/>
+    <hyperlink ref="CM28" r:id="rId67"/>
+    <hyperlink ref="CI29" r:id="rId68"/>
+    <hyperlink ref="CM29" r:id="rId69"/>
+    <hyperlink ref="CI30" r:id="rId70"/>
+    <hyperlink ref="CM30" r:id="rId71"/>
+    <hyperlink ref="CI31" r:id="rId72"/>
+    <hyperlink ref="CM31" r:id="rId73"/>
+    <hyperlink ref="CI32" r:id="rId74"/>
+    <hyperlink ref="CM32" r:id="rId75"/>
+    <hyperlink ref="CI33" r:id="rId76"/>
+    <hyperlink ref="CM33" r:id="rId77"/>
+    <hyperlink ref="CI34" r:id="rId78"/>
+    <hyperlink ref="CM34" r:id="rId79"/>
+    <hyperlink ref="CI35" r:id="rId80"/>
+    <hyperlink ref="CM35" r:id="rId81"/>
+    <hyperlink ref="CI36" r:id="rId82"/>
+    <hyperlink ref="CM36" r:id="rId83"/>
+    <hyperlink ref="CI37" r:id="rId84"/>
+    <hyperlink ref="CM37" r:id="rId85"/>
+    <hyperlink ref="CI38" r:id="rId86"/>
+    <hyperlink ref="CM38" r:id="rId87"/>
+    <hyperlink ref="CI39" r:id="rId88"/>
+    <hyperlink ref="CM39" r:id="rId89"/>
+    <hyperlink ref="CI40" r:id="rId90"/>
+    <hyperlink ref="CM40" r:id="rId91"/>
+    <hyperlink ref="CI41" r:id="rId92"/>
+    <hyperlink ref="CI42" r:id="rId93"/>
+    <hyperlink ref="CI43" r:id="rId94"/>
+    <hyperlink ref="CI44" r:id="rId95"/>
+    <hyperlink ref="CI45" r:id="rId96"/>
+    <hyperlink ref="CI46" r:id="rId97"/>
+    <hyperlink ref="CI47" r:id="rId98"/>
+    <hyperlink ref="CI48" r:id="rId99"/>
+    <hyperlink ref="CI49" r:id="rId100"/>
+    <hyperlink ref="CI50" r:id="rId101"/>
+    <hyperlink ref="CI51" r:id="rId102"/>
+    <hyperlink ref="CI52" r:id="rId103"/>
+    <hyperlink ref="CI53" r:id="rId104"/>
+    <hyperlink ref="CI54" r:id="rId105"/>
+    <hyperlink ref="CI55" r:id="rId106"/>
+    <hyperlink ref="CI56" r:id="rId107"/>
+    <hyperlink ref="CI57" r:id="rId108"/>
+    <hyperlink ref="CI58" r:id="rId109"/>
+    <hyperlink ref="CI59" r:id="rId110"/>
+    <hyperlink ref="CI60" r:id="rId111"/>
+    <hyperlink ref="CI61" r:id="rId112"/>
+    <hyperlink ref="CI62" r:id="rId113"/>
+    <hyperlink ref="CI63" r:id="rId114"/>
+    <hyperlink ref="CI64" r:id="rId115"/>
+    <hyperlink ref="CI65" r:id="rId116"/>
+    <hyperlink ref="CI66" r:id="rId117"/>
+    <hyperlink ref="CI67" r:id="rId118"/>
+    <hyperlink ref="CI68" r:id="rId119"/>
+    <hyperlink ref="CI69" r:id="rId120"/>
+    <hyperlink ref="CI70" r:id="rId121"/>
+    <hyperlink ref="CI71" r:id="rId122"/>
+    <hyperlink ref="CI72" r:id="rId123"/>
+    <hyperlink ref="CI73" r:id="rId124"/>
+    <hyperlink ref="CI74" r:id="rId125"/>
+    <hyperlink ref="CI75" r:id="rId126"/>
+    <hyperlink ref="CI76" r:id="rId127"/>
+    <hyperlink ref="CI77" r:id="rId128"/>
+    <hyperlink ref="CI78" r:id="rId129"/>
+    <hyperlink ref="CI79" r:id="rId130"/>
+    <hyperlink ref="CI80" r:id="rId131"/>
+    <hyperlink ref="CI81" r:id="rId132"/>
+    <hyperlink ref="CI82" r:id="rId133"/>
+    <hyperlink ref="CI83" r:id="rId134"/>
+    <hyperlink ref="CI84" r:id="rId135"/>
+    <hyperlink ref="CI85" r:id="rId136"/>
+    <hyperlink ref="CI86" r:id="rId137"/>
+    <hyperlink ref="CI87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="58">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -44557,6 +44575,8 @@
     <tablePart r:id="rId192"/>
     <tablePart r:id="rId193"/>
     <tablePart r:id="rId194"/>
+    <tablePart r:id="rId195"/>
+    <tablePart r:id="rId196"/>
   </tableParts>
 </worksheet>
 </file>
@@ -44568,50 +44588,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="B1" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="B2" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="B3" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="B4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="B5" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B6" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
     </row>
   </sheetData>
@@ -48609,7 +48629,7 @@
       <formula1>'Codelijsten'!$CI$4:$CI$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$CK$4:$CK$12</formula1>
+      <formula1>'Codelijsten'!$CK$4:$CK$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -48731,58 +48751,58 @@
   <sheetData>
     <row r="1" spans="1:74" hidden="1">
       <c r="A1" s="7" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>77</v>
@@ -48791,16 +48811,16 @@
         <v>79</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>308</v>
@@ -48824,49 +48844,49 @@
         <v>1345</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>349</v>
@@ -48893,13 +48913,13 @@
         <v>316</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>55</v>
@@ -48981,7 +49001,7 @@
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -49008,13 +49028,13 @@
         <v>1345</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -49041,7 +49061,7 @@
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -49080,7 +49100,7 @@
         <v>289</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -49094,7 +49114,7 @@
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -49122,7 +49142,7 @@
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -49154,10 +49174,10 @@
         <v>305</v>
       </c>
       <c r="BC3" s="8" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="BD3" s="8" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="BE3" s="1" t="s">
         <v>32</v>
@@ -49223,7 +49243,7 @@
         <v>347</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -49370,58 +49390,58 @@
     </row>
     <row r="7" spans="1:74">
       <c r="A7" s="7" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>77</v>
@@ -49430,16 +49450,16 @@
         <v>79</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>308</v>
@@ -49463,49 +49483,49 @@
         <v>1345</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="AG7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="AU7" s="1" t="s">
         <v>349</v>
@@ -49532,13 +49552,13 @@
         <v>316</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="BE7" s="1" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="BF7" s="1" t="s">
         <v>55</v>

--- a/templates/productie/productie_bodem_template.xlsx
+++ b/templates/productie/productie_bodem_template.xlsx
@@ -6133,13 +6133,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:28:43.640697</t>
+    <t>2026-05-19 14:52:36.714041</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
